--- a/RaidenDemo/文档/配置表/StageResource.xlsx
+++ b/RaidenDemo/文档/配置表/StageResource.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rca010be54af74266"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re13710146c964eee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1238,27 +1238,27 @@
       </x:c>
       <x:c r="I1" s="21" t="inlineStr">
         <x:is>
-          <x:t>supplyFirstDelayMs</x:t>
+          <x:t xml:space="preserve">supplyFirstDelayMs</x:t>
         </x:is>
       </x:c>
       <x:c r="J1" s="21" t="inlineStr">
         <x:is>
-          <x:t>supplyIntervalMs</x:t>
+          <x:t xml:space="preserve">supplyIntervalMs</x:t>
         </x:is>
       </x:c>
       <x:c r="K1" s="21" t="inlineStr">
         <x:is>
-          <x:t>supplyItemIds</x:t>
+          <x:t xml:space="preserve">supplyItemIds</x:t>
         </x:is>
       </x:c>
       <x:c r="L1" s="21" t="inlineStr">
         <x:is>
-          <x:t>waveIntervalMs</x:t>
+          <x:t xml:space="preserve">waveIntervalMs</x:t>
         </x:is>
       </x:c>
       <x:c r="M1" s="21" t="inlineStr">
         <x:is>
-          <x:t>victoryDelayMs</x:t>
+          <x:t xml:space="preserve">victoryDelayMs</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1289,27 +1289,27 @@
       </x:c>
       <x:c r="I2" s="22" t="inlineStr">
         <x:is>
-          <x:t>补给首次延迟毫秒</x:t>
+          <x:t xml:space="preserve">补给首次延迟毫秒</x:t>
         </x:is>
       </x:c>
       <x:c r="J2" s="22" t="inlineStr">
         <x:is>
-          <x:t>补给间隔毫秒</x:t>
+          <x:t xml:space="preserve">补给间隔毫秒</x:t>
         </x:is>
       </x:c>
       <x:c r="K2" s="22" t="inlineStr">
         <x:is>
-          <x:t>补给道具顺序</x:t>
+          <x:t xml:space="preserve">补给道具顺序</x:t>
         </x:is>
       </x:c>
       <x:c r="L2" s="22" t="inlineStr">
         <x:is>
-          <x:t>编队间隔毫秒</x:t>
+          <x:t xml:space="preserve">编队间隔毫秒</x:t>
         </x:is>
       </x:c>
       <x:c r="M2" s="22" t="inlineStr">
         <x:is>
-          <x:t>胜利结算等待毫秒</x:t>
+          <x:t xml:space="preserve">胜利结算等待毫秒</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1340,27 +1340,27 @@
       </x:c>
       <x:c r="I3" s="21" t="inlineStr">
         <x:is>
-          <x:t>int</x:t>
+          <x:t xml:space="preserve">int</x:t>
         </x:is>
       </x:c>
       <x:c r="J3" s="21" t="inlineStr">
         <x:is>
-          <x:t>int</x:t>
+          <x:t xml:space="preserve">int</x:t>
         </x:is>
       </x:c>
       <x:c r="K3" s="21" t="inlineStr">
         <x:is>
-          <x:t>(list#sep=,),int</x:t>
+          <x:t xml:space="preserve">(list#sep=,),int</x:t>
         </x:is>
       </x:c>
       <x:c r="L3" s="21" t="inlineStr">
         <x:is>
-          <x:t>int</x:t>
+          <x:t xml:space="preserve">int</x:t>
         </x:is>
       </x:c>
       <x:c r="M3" s="21" t="inlineStr">
         <x:is>
-          <x:t>int</x:t>
+          <x:t xml:space="preserve">int</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1373,7 +1373,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
-        <x:v>101,102,103,104</x:v>
+        <x:v>101,102,103,104,105</x:v>
       </x:c>
       <x:c r="E4" s="24" t="n">
         <x:v>402</x:v>
@@ -1395,7 +1395,7 @@
       </x:c>
       <x:c r="K4" s="32" t="inlineStr">
         <x:is>
-          <x:t>1,2,3,4,5,6,7</x:t>
+          <x:t xml:space="preserve">1,2,3,4,5,6,7</x:t>
         </x:is>
       </x:c>
       <x:c r="L4" s="27">
@@ -1436,7 +1436,7 @@
       </x:c>
       <x:c r="K5" s="32" t="inlineStr">
         <x:is>
-          <x:t>1,2,3,4,5,6,7</x:t>
+          <x:t xml:space="preserve">1,2,3,4,5,6,7</x:t>
         </x:is>
       </x:c>
       <x:c r="L5" s="27">
@@ -1477,7 +1477,7 @@
       </x:c>
       <x:c r="K6" s="32" t="inlineStr">
         <x:is>
-          <x:t>1,2,3,4,5,6,7</x:t>
+          <x:t xml:space="preserve">1,2,3,4,5,6,7</x:t>
         </x:is>
       </x:c>
       <x:c r="L6" s="27">
@@ -1518,7 +1518,7 @@
       </x:c>
       <x:c r="K7" s="32" t="inlineStr">
         <x:is>
-          <x:t>1,2,3,4,5,6,7</x:t>
+          <x:t xml:space="preserve">1,2,3,4,5,6,7</x:t>
         </x:is>
       </x:c>
       <x:c r="L7" s="27">
@@ -1559,7 +1559,7 @@
       </x:c>
       <x:c r="K8" s="32" t="inlineStr">
         <x:is>
-          <x:t>1,2,3,4,5,6,7</x:t>
+          <x:t xml:space="preserve">1,2,3,4,5,6,7</x:t>
         </x:is>
       </x:c>
       <x:c r="L8" s="27">
@@ -1600,7 +1600,7 @@
       </x:c>
       <x:c r="K9" s="32" t="inlineStr">
         <x:is>
-          <x:t>1,2,3,4,5,6,7</x:t>
+          <x:t xml:space="preserve">1,2,3,4,5,6,7</x:t>
         </x:is>
       </x:c>
       <x:c r="L9" s="27">
@@ -1641,7 +1641,7 @@
       </x:c>
       <x:c r="K10" s="32" t="inlineStr">
         <x:is>
-          <x:t>1,2,3,4,5,6,7</x:t>
+          <x:t xml:space="preserve">1,2,3,4,5,6,7</x:t>
         </x:is>
       </x:c>
       <x:c r="L10" s="27">
@@ -1682,7 +1682,7 @@
       </x:c>
       <x:c r="K11" s="32" t="inlineStr">
         <x:is>
-          <x:t>1,2,3,4,5,6,7</x:t>
+          <x:t xml:space="preserve">1,2,3,4,5,6,7</x:t>
         </x:is>
       </x:c>
       <x:c r="L11" s="27">
@@ -1723,7 +1723,7 @@
       </x:c>
       <x:c r="K12" s="32" t="inlineStr">
         <x:is>
-          <x:t>1,2,3,4,5,6,7</x:t>
+          <x:t xml:space="preserve">1,2,3,4,5,6,7</x:t>
         </x:is>
       </x:c>
       <x:c r="L12" s="27">
@@ -1764,7 +1764,7 @@
       </x:c>
       <x:c r="K13" s="32" t="inlineStr">
         <x:is>
-          <x:t>1,2,3,4,5,6,7</x:t>
+          <x:t xml:space="preserve">1,2,3,4,5,6,7</x:t>
         </x:is>
       </x:c>
       <x:c r="L13" s="27">
